--- a/SFT/SFT_Runs/llm_results.xlsx
+++ b/SFT/SFT_Runs/llm_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WINDOWS 11\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_3D528A4A97511D012E00A7CB6062C45C5FFD5D13" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50EB3EEE-1352-433C-8094-52DFACAAE6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blue Test" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,7 @@
     <sheet name="Red Test" sheetId="4" r:id="rId4"/>
     <sheet name="Red Val" sheetId="5" r:id="rId5"/>
     <sheet name="Red - Metric Explanations" sheetId="6" r:id="rId6"/>
+    <sheet name="SFT Process Explained" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="331">
   <si>
     <t>Blue LLM — Test Set Results</t>
   </si>
@@ -80,7 +81,7 @@
     <t>Blue LLM — Custom Evaluation Metrics: Function-by-Function Explanation</t>
   </si>
   <si>
-    <t>Prepared to document the custom evaluation pipeline used to score the Defense (Blue) model across three fine-tuned checkpoints: Qwen3-8B, Qwen2.5-7B-Instruct, and Meta-Llama-3.1-8B-Instruct. Mirrors the structure/logic of the Red (Attack) evaluation pipeline, with 'attack' replaced by 'defense' as the section label and metric name throughout. Covers every helper function, the model-specific variations between the three implementations, and the final metrics reported in 'Blue Test' / 'Blue Val'.</t>
+    <t>Prepared to document the custom evaluation pipeline used to score the Defense (Blue) model across three fine-tuned checkpoints: Qwen3-8B, Qwen2.5-7B-Instruct, and Meta-Llama-3.1-8B-Instruct.</t>
   </si>
   <si>
     <t>1.  Why This Pipeline Exists</t>
@@ -128,7 +129,7 @@
   </si>
   <si>
     <t>1) Casts input to str, returns '' for None.
-2) Strips any &lt;think&gt;...&lt;/think&gt; block the model may have emitted.
+2) Strips any &lt;think&gt;...&lt;/think&gt;or any model specific token block the model may have emitted.
 3) Strips markdown bold (**x**), underline-bold (__x__) and inline code (`x`), keeping only the inner text.
 4) Normalizes CRLF/CR line endings to LF.
 5) Collapses 3+ blank lines down to a single blank line.
@@ -145,7 +146,7 @@
     <t>Base version - no special-token stripping. Comment simply says 'Remove thinking block'.</t>
   </si>
   <si>
-    <t>Same base version, but the comment explicitly notes the &lt;think&gt; block removal is 'specific to Qwen Models' - otherwise byte-for-byte identical to the Qwen3 implementation.</t>
+    <t>Same base version,byte-for-byte identical to the Qwen3 implementation.</t>
   </si>
   <si>
     <t>Adds one extra line not present in the other two: re.sub(r"&lt;\|.*?\|&gt;", "", text) - strips leftover Llama-3.1 control tokens such as &lt;|eot_id|&gt; or &lt;|start_header_id|&gt;, applied right after the &lt;think&gt;-block removal and before markdown stripping. Also explicitly does 'import re' at the top of the cell.</t>
@@ -486,7 +487,7 @@
     <t>Red LLM — Custom Evaluation Metrics: Function-by-Function Explanation</t>
   </si>
   <si>
-    <t>Prepared to document the custom evaluation pipeline used to score the Attack (Red) model across three fine-tuned checkpoints: Qwen3-8B, Qwen2.5-7B-Instruct, and Meta-Llama-3.1-8B-Instruct. Covers every helper function in Cell 17, the model-specific variations between the three implementations, and the final metrics reported in 'Red Test' / 'Red Val'.</t>
+    <t>Prepared to document the custom evaluation pipeline used to score the Attack (Red) model across three fine-tuned checkpoints: Qwen3-8B, Qwen2.5-7B-Instruct, and Meta-Llama-3.1-8B-Instruct.</t>
   </si>
   <si>
     <t>Each fine-tuned LLM is prompted to output a structured, four-part answer for a given red-team scenario:
@@ -665,6 +666,531 @@
   </si>
   <si>
     <t>Note: Despite these small parsing differences, all three checkpoints are scored through the exact same evaluate_predictions() function, so the seven headline metrics in the 'Red Test' / 'Red Val' sheets remain directly comparable across models.</t>
+  </si>
+  <si>
+    <t>SFT Training Pipeline — Input Prompts, Loss Function &amp; Model Output Explained</t>
+  </si>
+  <si>
+    <t>Prepared to walk through exactly what happens during Supervised Fine-Tuning (SFT) of the Red (attacker) LoRA adapter on Qwen2.5-7B-Instruct: the raw training sample, what text the model is actually shown, how the loss is computed, and what the model is trained to produce. Based directly on the qwen25_red.ipynb training notebook and a real sample from train_red.jsonl (scenario_001).</t>
+  </si>
+  <si>
+    <t>1.  What SFT Is Doing Here</t>
+  </si>
+  <si>
+    <t>•  Red and Blue start as the exact same frozen base model — Qwen2.5-7B-Instruct, loaded in 4-bit / QLoRA.
+•  SFT does NOT touch the base weights at all. It only trains a small LoRA adapter (rank 32, alpha 64) bolted onto the attention + MLP projection layers (q/k/v/o_proj, gate/up/down_proj).
+•  For every scenario, the model is shown a conversation with 2 given turns — SYSTEM (persona + task rules) and USER (codebase + scenario) — plus 1 target turn it must learn to reproduce — ASSISTANT (the correct Attack + Reasoning + Wrong Actions + Wrong Action Reasoning).
+•  This is imitation learning: the model is never asked to discover the vulnerability on its own during SFT. It is taught the correct answer directly, the same way a student memorises worked examples before ever being tested.</t>
+  </si>
+  <si>
+    <t>2.  Training Configuration (from qwen25_red.ipynb, Cell 3)</t>
+  </si>
+  <si>
+    <t>Parameter</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>What It Controls</t>
+  </si>
+  <si>
+    <t>BASE_MODEL</t>
+  </si>
+  <si>
+    <t>unsloth/Qwen2.5-7B-Instruct</t>
+  </si>
+  <si>
+    <t>The single frozen base model shared by both Red and Blue.
+•  Only its LoRA adapter differs per role.</t>
+  </si>
+  <si>
+    <t>MAX_SEQ_LENGTH</t>
+  </si>
+  <si>
+    <t>6144 tokens</t>
+  </si>
+  <si>
+    <t>Hard cap on prompt+response length.
+•  Longer scenarios get truncated by the tokenizer past this.</t>
+  </si>
+  <si>
+    <t>LOAD_IN_4BIT</t>
+  </si>
+  <si>
+    <t>True (QLoRA)</t>
+  </si>
+  <si>
+    <t>Base weights quantized to 4-bit to fit training on 1x 24GB GPU.
+•  LoRA adapters stay in higher precision.</t>
+  </si>
+  <si>
+    <t>LORA_RANK / LORA_ALPHA</t>
+  </si>
+  <si>
+    <t>32 / 64</t>
+  </si>
+  <si>
+    <t>Rank = size of the trainable low-rank matrices per layer.
+•  Alpha scales their contribution (effective scale = alpha/rank = 2x).</t>
+  </si>
+  <si>
+    <t>LORA_DROPOUT</t>
+  </si>
+  <si>
+    <t>0.05</t>
+  </si>
+  <si>
+    <t>Randomly zeroes 5% of LoRA activations during training.
+•  Reduces overfitting on ~100 scenarios.</t>
+  </si>
+  <si>
+    <t>TARGET_MODULES</t>
+  </si>
+  <si>
+    <t>q/k/v/o_proj, gate/up/down_proj</t>
+  </si>
+  <si>
+    <t>All 4 attention projections get a LoRA adapter.
+•  All 3 MLP projections get a LoRA adapter.
+•  This is a fairly wide/expressive adapter overall.</t>
+  </si>
+  <si>
+    <t>BATCH_SIZE / GRAD_ACCUM</t>
+  </si>
+  <si>
+    <t>1 / 16</t>
+  </si>
+  <si>
+    <t>Only 1 sample fits in memory at a time (long contexts).
+•  Gradients accumulate over 16 steps before each update.
+•  Effective batch size = 16.</t>
+  </si>
+  <si>
+    <t>EPOCHS</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Every training scenario is shown to the model 3 full times.</t>
+  </si>
+  <si>
+    <t>LEARNING_RATE</t>
+  </si>
+  <si>
+    <t>2e-4</t>
+  </si>
+  <si>
+    <t>Step size for AdamW updates to the LoRA weights only.
+•  Base weights receive zero gradient.</t>
+  </si>
+  <si>
+    <t>LR_SCHEDULER</t>
+  </si>
+  <si>
+    <t>cosine, warmup_ratio=0.05</t>
+  </si>
+  <si>
+    <t>LR ramps up for the first 5% of steps.
+•  Then decays smoothly along a cosine curve to ~0 by the final step.</t>
+  </si>
+  <si>
+    <t>OPTIM</t>
+  </si>
+  <si>
+    <t>adamw_8bit</t>
+  </si>
+  <si>
+    <t>8-bit AdamW — identical optimizer math to standard AdamW.
+•  Optimizer states are quantized to save GPU memory.</t>
+  </si>
+  <si>
+    <t>WEIGHT_DECAY</t>
+  </si>
+  <si>
+    <t>0.01</t>
+  </si>
+  <si>
+    <t>L2 penalty added to the loss.
+•  Discourages LoRA weights from growing unboundedly large.</t>
+  </si>
+  <si>
+    <t>Precision</t>
+  </si>
+  <si>
+    <t>bf16 (fp16 fallback)</t>
+  </si>
+  <si>
+    <t>Forward/backward pass computed in 16-bit.
+•  Weight updates accumulated in fp32.</t>
+  </si>
+  <si>
+    <t>Train / Val / Test split</t>
+  </si>
+  <si>
+    <t>80% / 10% / 10%</t>
+  </si>
+  <si>
+    <t>Dataset shuffled (seed=42), then split.
+•  Validation → eval_loss / best-checkpoint selection.
+•  Test → fully held out, used only for final reporting.</t>
+  </si>
+  <si>
+    <t>3.  The Raw Training Sample — the "messages" Array in train_red.jsonl</t>
+  </si>
+  <si>
+    <t>•  Each line of train_red.jsonl is one JSON object: {"messages": [ {role, content}, {role, content}, {role, content} ]}.
+•  There are always exactly 3 turns, in this fixed order.
+•  The trainer never sees metadata.json fields (valid_attacks / optimal_attack, etc.) inside this array — those are grading-only and are withheld from the prompt.</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Who Writes It</t>
+  </si>
+  <si>
+    <t>Predicted By The Model?</t>
+  </si>
+  <si>
+    <t>system</t>
+  </si>
+  <si>
+    <t>Fixed persona text, identical across all scenarios</t>
+  </si>
+  <si>
+    <t>•  States WHO the model is (Red Team analyst).
+•  States HOW to reason — structured architectural analysis, boundary identification, eliminate competing hypotheses — before seeing the scenario.</t>
+  </si>
+  <si>
+    <t>No — always given as context.</t>
+  </si>
+  <si>
+    <t>user</t>
+  </si>
+  <si>
+    <t>Per-scenario, built by the compile script from scenario.md + files/*</t>
+  </si>
+  <si>
+    <t>•  The actual task: application description + business context.
+•  Plus, depending on the example variant: full codebase / relevant files only / condensed audit view.</t>
+  </si>
+  <si>
+    <t>assistant</t>
+  </si>
+  <si>
+    <t>The gold-label answer written for this scenario</t>
+  </si>
+  <si>
+    <t>•  The correct output: Attack name + step-by-step Reasoning + Wrong Actions + Wrong Action Reasoning.
+•  Written in the frozen 4-part output format.</t>
+  </si>
+  <si>
+    <t>YES — this is the ONLY turn the model is trained to generate. The loss function scores this turn only.</t>
+  </si>
+  <si>
+    <t>4.  Full Worked Example — What The Model Actually Sees (scenario_001)</t>
+  </si>
+  <si>
+    <t>•  Pulled directly from the notebook's dataset preview (Cell 6 output).
+•  This is the literal text content of each message BEFORE the chat template wraps it — i.e. what a human labeller/reviewer reads.
+•  Long codebase content inside the user turn is injected at JSONL-compile time from the scenario's files/ directory.</t>
+  </si>
+  <si>
+    <t>Turn</t>
+  </si>
+  <si>
+    <t>Content (excerpt as logged by the notebook)</t>
+  </si>
+  <si>
+    <t>SYSTEM</t>
+  </si>
+  <si>
+    <t>•  You are a Red Team cybersecurity analyst specializing in architectural security assessments of enterprise software systems.
+•  Objective: identify the single most effective attack supported by the business context, architecture, workflow, trust boundaries, and source code.
+•  Perform a structured architectural analysis before reaching a conclusion. During analysis:
+    1. Identify the canonical security boundary of the application.
+    2. Follow the end-to-end business workflow.
+    3. Track how security-critical information is transformed between components.
+    4. Distinguish architectural weaknesses from implementation details.
+    5. Eliminate competing attack hypotheses before selecting the final attack.
+    6. Base every conclusion only on the supplied information. Do not assume unde... [truncated in notebook log preview]</t>
+  </si>
+  <si>
+    <t>USER</t>
+  </si>
+  <si>
+    <t>•  Analyze the following enterprise codebase as an experienced Red Team security analyst.
+•  Carefully reason through the application architecture, data flow, trust relationships, and implementation details before determining the most effective attack.
+•  Base your reasoning only on the provided material.
+•  APPLICATION DESCRIPTION — Application ID: scenario_001
+•  Description: A Flask web application uses JWT-based authentication.
+    - The signing secret is hardcoded as a weak, guessable string.
+    - Tokens are issued at /login and checked at /admin.
+    - verify_token() silently returns None on failure.
+    - Tokens carry no expiry claim despite TOKEN_EXPIRY_SECONDS being configure... [truncated in notebook log preview]
+•  (Full prompt also includes the injected file contents, e.g. app.py, config.py, per the scenario's files/ tier.)</t>
+  </si>
+  <si>
+    <t>ASSISTANT
+(training target)</t>
+  </si>
+  <si>
+    <t>•  Attack: jwt_forgery
+•  Reasoning:
+    1. The JWT signing secret is hardcoded as "password123" in config.py — trivially guessable, and can also be brute-forced offline against any captured token.
+    2. create_token() builds payloads with arbitrary username and role fields with no server-side binding to real users — forging a token with role "admin" is straightforward.
+    3. The /admin endpoint calls verify_token() and checks only the role claim — no session lookup, no token revocation check, no expiry enforcement despite TOKEN_EXPIRY_SECONDS being defined.
+    4. A forged token with {"username": "attacker", "role": "admin"} signed with the known secret will pass all checks.
+•  Wrong Actions: [additional incorrect actions the model must also name — e.g. credential_stuffing, brute_force]
+•  Wrong Action Reasoning: [explanation of why each listed action fails, per the frozen 4-part output format]</t>
+  </si>
+  <si>
+    <t>•  Per red_sft.json prompt-diversity rules, three USER variants exist per scenario:
+•  1. Full codebase / code-review framing.
+•  2. Relevant-files-only / threat-modeling framing.
+•  3. Condensed audit view / concrete attack-path framing with specific endpoints and IDs.
+•  Each variant is paired with differently-styled Reasoning in the ASSISTANT turn — the model sees the same vulnerability argued three different ways rather than memorising one fixed phrasing.</t>
+  </si>
+  <si>
+    <t>5.  Chat Template Formatting — tokenizer.apply_chat_template() (Cell 9)</t>
+  </si>
+  <si>
+    <t>•  The 3-turn messages[] list above is not fed to the model as raw JSON.
+•  formatting_prompts_func() calls tokenizer.apply_chat_template(conversation, tokenize=False, add_generation_prompt=False).
+•  This converts the list into ONE single string using Qwen2.5's ChatML-style special tokens.
+•  The wrapped string is stored in a new "text" field — this is what SFTTrainer actually tokenizes and trains on.</t>
+  </si>
+  <si>
+    <t>&lt;|im_start|&gt;system
+You are a Red Team cybersecurity analyst specializing in architectural security assessments...
+&lt;|im_end|&gt;
+&lt;|im_start|&gt;user
+Analyze the following enterprise codebase as an experienced Red Team security analyst...
+&lt;|im_end|&gt;
+&lt;|im_start|&gt;assistant
+Attack: jwt_forgery
+Reasoning: The JWT signing secret is hardcoded as "password123" in config.py...
+&lt;|im_end|&gt;</t>
+  </si>
+  <si>
+    <t>•  &lt;|im_start|&gt; / &lt;|im_end|&gt; are special tokens marking where each role's turn begins and ends.
+•  The tokenizer reserves fixed token IDs for them so the model can always tell, at the token level, whose turn it is.
+•  This is exactly the boundary the loss-masking step below relies on.</t>
+  </si>
+  <si>
+    <t>6.  Loss Masking — train_on_responses_only() (Cell 10)</t>
+  </si>
+  <si>
+    <t>•  By default, a causal LM trained on the full formatted string would also be penalised for failing to predict the SYSTEM and USER text — nonsensical, since that text is given, not generated.
+•  train_on_responses_only(trainer, instruction_part="&lt;|im_start|&gt;user\n", response_part="&lt;|im_start|&gt;assistant\n") post-processes the tokenized batch.
+•  It sets every label BEFORE the assistant marker to -100 (PyTorch's "ignore this token" index for cross-entropy).
+•  Only the tokens that make up the ASSISTANT turn keep their real label ids.</t>
+  </si>
+  <si>
+    <t>Segment</t>
+  </si>
+  <si>
+    <t>Included In Loss?</t>
+  </si>
+  <si>
+    <t>Why</t>
+  </si>
+  <si>
+    <t>&lt;|im_start|&gt;system ... &lt;|im_end|&gt;</t>
+  </si>
+  <si>
+    <t>Masked (label = -100)</t>
+  </si>
+  <si>
+    <t>•  Fixed persona text.
+•  Model must be able to condition on it, never generate it.</t>
+  </si>
+  <si>
+    <t>&lt;|im_start|&gt;user ... &lt;|im_end|&gt;</t>
+  </si>
+  <si>
+    <t>•  The scenario/codebase is given input, not something to predict.
+•  Including it in the loss would reward memorising codebases verbatim instead of reasoning.</t>
+  </si>
+  <si>
+    <t>&lt;|im_start|&gt;assistant\n</t>
+  </si>
+  <si>
+    <t>•  The role tag is a fixed template token.
+•  No need to score the model on generating it.</t>
+  </si>
+  <si>
+    <t>Attack: ... Reasoning: ... &lt;|im_end|&gt;</t>
+  </si>
+  <si>
+    <t>UNMASKED — real labels</t>
+  </si>
+  <si>
+    <t>•  This is the only span the model is trained to produce.
+•  Every gradient update comes from how well the model predicted these tokens.</t>
+  </si>
+  <si>
+    <t>7.  Loss Function — Masked Causal-LM Cross-Entropy</t>
+  </si>
+  <si>
+    <t>•  SFTTrainer (TRL) uses the standard next-token-prediction cross-entropy loss — the same loss every GPT-style decoder is pretrained with.
+•  It is averaged ONLY over the unmasked (assistant-turn) tokens produced by train_on_responses_only().
+•  The base model's weights are frozen (requires_grad=False).
+•  The only parameters that receive a gradient are the LoRA A/B matrices injected into the 7 target modules.</t>
+  </si>
+  <si>
+    <t>Loss  =  - (1 / N) * SUM over t in RESPONSE_TOKENS of  log P( y_t | y_&lt;t , x ; theta_LoRA )
+  x            = all system + user tokens (frozen context the model conditions on, never scored)
+  y_1 ... y_T  = the assistant turn's token sequence (Attack / Reasoning / Wrong Actions / Wrong Action Reasoning)
+  y_&lt;t         = every assistant token generated before position t (causal / left-to-right masking, standard decoder-only attention)
+  N            = number of UNMASKED tokens (only assistant-turn tokens; masked positions contribute 0 and are excluded from the average)
+  theta_LoRA   = trainable parameters (LoRA rank-32 A/B matrices only — base Qwen2.5 weights stay frozen throughout)
+Per-token term:
+  - log P(y_t | ...) comes from a softmax over the full ~152k-token Qwen2.5 vocabulary at each position.
+  - Compared against the single correct next token via standard multi-class cross-entropy.
+  - nn.CrossEntropyLoss, ignore_index=-100, so masked positions are skipped automatically.</t>
+  </si>
+  <si>
+    <t>•  Optimizer: AdamW (8-bit, adamw_8bit) updates theta_LoRA using this loss's gradient.
+•  Schedule: learning rate 2e-4, cosine decay after a 5% linear warmup, weight_decay=0.01 as an added L2 term.
+•  "Training Loss" in the Red Test sheet (e.g. 1.351 for Qwen2.5-7B-Instruct) = this cross-entropy averaged across all training steps of the final epoch.
+•  "Validation Loss (Best epoch)" in the Red Val sheet (e.g. 1.215) = same formula evaluated on the held-out validation split, at the epoch that minimised it.
+•  Selection rule: metric_for_best_model="eval_loss", greater_is_better=False, load_best_model_at_end=True — that checkpoint is the one saved as best_adapter.</t>
+  </si>
+  <si>
+    <t>8.  Model Output — What The Trained Model Generates At Inference</t>
+  </si>
+  <si>
+    <t>•  After training, FastLanguageModel.for_inference(model) switches the model to generation mode (model.config.use_cache restored to True).
+•  generate_response() re-applies the SAME chat template but with add_generation_prompt=True, appending an empty "&lt;|im_start|&gt;assistant\n" and asking the model to complete it.
+•  Because SFT only ever trained on the assistant span, the model has learned to continue that span in exactly the 4-part structured format below.
+•  This structure is what structure_correct() / Structure Score checks for at eval time.</t>
+  </si>
+  <si>
+    <t>Output Section</t>
+  </si>
+  <si>
+    <t>Model Must Generate</t>
+  </si>
+  <si>
+    <t>Attack:</t>
+  </si>
+  <si>
+    <t>•  A single-line attack/vulnerability name, e.g. "jwt_forgery", "sql_injection_union".
+•  Scored by exact-match Attack Accuracy after normalize().</t>
+  </si>
+  <si>
+    <t>Reasoning:</t>
+  </si>
+  <si>
+    <t>•  A free-text, multi-step justification tracing the vulnerability through the code/architecture (cross-file, boundary-aware, per Section 1's system prompt).
+•  Scored by embedding cosine similarity (Reasoning Similarity) against the gold reasoning, not exact match.</t>
+  </si>
+  <si>
+    <t>Wrong Actions:</t>
+  </si>
+  <si>
+    <t>•  A bulleted list of plausible-but-incorrect actions Red considered and rejected.
+•  Scored as an order-independent SET match (Wrong Actions Accuracy) against the gold set.</t>
+  </si>
+  <si>
+    <t>Wrong Action Reasoning:</t>
+  </si>
+  <si>
+    <t>•  Free text explaining why each listed wrong action fails/is inferior.
+•  Scored by embedding cosine similarity (Wrong Action Reasoning Similarity), same mechanism as Reasoning.</t>
+  </si>
+  <si>
+    <t>•  Generation settings: DO_SAMPLE=False (greedy decoding), TEMPERATURE=0.1, TOP_P=0.95, MAX_NEW_TOKENS=1024.
+•  i.e. near-deterministic decoding — the same input reliably reproduces the same output.
+•  This is what makes the Test/Val comparisons in the other sheets reproducible run-to-run.</t>
+  </si>
+  <si>
+    <t>9.  End-to-End Flow, Start To Finish</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>What Happens</t>
+  </si>
+  <si>
+    <t>1. Author scenario</t>
+  </si>
+  <si>
+    <t>•  scenario_001/files/*, scenario.md, metadata.json, red_sft.json, blue_sft.json are written (hand or LLM-assisted).
+•  Grounded in real vulnerable code.</t>
+  </si>
+  <si>
+    <t>2. Compile</t>
+  </si>
+  <si>
+    <t>•  compile_dataset.py reads every scenario's red_sft.json.
+•  Injects the relevant files/ content into the user turn.
+•  Writes one line per example into train_red.jsonl as {"messages": [system, user, assistant]}.</t>
+  </si>
+  <si>
+    <t>3. Load &amp; split</t>
+  </si>
+  <si>
+    <t>•  load_dataset() reads train_red.jsonl.
+•  dataset.shuffle(seed=42).train_test_split() produces 80/10/10 train/val/test.</t>
+  </si>
+  <si>
+    <t>4. Chat-template</t>
+  </si>
+  <si>
+    <t>•  formatting_prompts_func() runs tokenizer.apply_chat_template() on every example.
+•  Turns the 3-turn list into one ChatML string with &lt;|im_start|&gt;/&lt;|im_end|&gt; tokens.
+•  Stored in a "text" field.</t>
+  </si>
+  <si>
+    <t>5. Tokenize + mask</t>
+  </si>
+  <si>
+    <t>•  SFTTrainer tokenizes "text".
+•  train_on_responses_only() sets labels to -100 for every token before "&lt;|im_start|&gt;assistant\n".
+•  Only the assistant span stays unmasked.</t>
+  </si>
+  <si>
+    <t>6. Forward + loss</t>
+  </si>
+  <si>
+    <t>•  Model predicts a next-token distribution at every position.
+•  Masked-average cross-entropy (Section 7) is computed only over the unmasked assistant tokens.</t>
+  </si>
+  <si>
+    <t>7. Backward + update</t>
+  </si>
+  <si>
+    <t>•  Gradients flow only into the LoRA A/B matrices (base frozen).
+•  AdamW-8bit applies the update at LEARNING_RATE=2e-4 on a cosine schedule.
+•  Once every 16 accumulated steps (effective batch 16).</t>
+  </si>
+  <si>
+    <t>8. Repeat x3 epochs</t>
+  </si>
+  <si>
+    <t>•  Every scenario is seen 3 times.
+•  eval_loss computed on the validation split at the end of each epoch.
+•  Epoch with the lowest eval_loss is kept (best_adapter).</t>
+  </si>
+  <si>
+    <t>9. Inference</t>
+  </si>
+  <si>
+    <t>•  FastLanguageModel.for_inference(model) + generate_response() reproduce the ChatML prompt (system+user only, add_generation_prompt=True).
+•  Greedily decodes the model's completion of the assistant turn.</t>
+  </si>
+  <si>
+    <t>10. Score</t>
+  </si>
+  <si>
+    <t>•  Generated text is parsed (clean_prediction → normalize/extract_*).
+•  Compared against the gold assistant turn.
+•  Produces the 7 metrics shown in the Red Test / Red Val sheets.</t>
   </si>
 </sst>
 </file>
@@ -859,8 +1385,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -922,6 +1457,9 @@
     <xf numFmtId="2" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -942,6 +1480,12 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1215,136 +1759,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
     </row>
     <row r="3" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="17" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="19">
         <v>1.47904272306533</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="19">
         <v>1.38362985565549</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="20">
         <v>1.22373788129716</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="21">
         <v>0.107142857142857</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="21">
         <v>0.160714285714286</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="22">
         <v>0.214285714285714</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="23">
         <v>6144</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="23">
         <v>6144</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="24">
         <v>6144</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="21">
         <v>0.80897223949432395</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="21">
         <v>0.81399482488632202</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="22">
         <v>0.82223117351532005</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="21">
         <v>3.5714285714285698E-2</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="21">
         <v>5.3571428571428603E-2</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="22">
         <v>7.1428571428571397E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="22">
         <v>0.387194663286209</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="21">
         <v>0.36281907558441201</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="21">
         <v>0.37952110171318099</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="22">
         <v>0.96428571428571397</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="21">
         <v>0.85714285714285698</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="21">
         <v>0.92857142857142905</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="25">
         <v>61.411198015723897</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="26">
         <v>38.575837565319901</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="25">
         <v>42.587835350206902</v>
       </c>
     </row>
@@ -1367,136 +1911,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
     </row>
     <row r="3" spans="1:4" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="17" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="19">
         <v>1.268632</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="19">
         <v>1.3113360000000001</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="20">
         <v>1.23929</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="21">
         <v>0.145454545454545</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="21">
         <v>0.25454545454545502</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="22">
         <v>0.381818181818182</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="23">
         <v>6144</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="23">
         <v>6144</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="24">
         <v>6144</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="21">
         <v>0.80996769666671797</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="21">
         <v>0.81798952817916903</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="22">
         <v>0.825919508934021</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="21">
         <v>9.0909090909090898E-2</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="21">
         <v>0.109090909090909</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="22">
         <v>0.12727272727272701</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="19">
+      <c r="B9" s="22">
         <v>0.38176450133323703</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="21">
         <v>0.34945920109748801</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="21">
         <v>0.30637899041175798</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="22">
         <v>0.87272727272727302</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="21">
         <v>0.78181818181818197</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="21">
         <v>0.81818181818181801</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="25">
         <v>66.410535990108102</v>
       </c>
-      <c r="C11" s="23">
+      <c r="C11" s="26">
         <v>41.899133235758001</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="25">
         <v>45.763585112311603</v>
       </c>
     </row>
@@ -1519,608 +2063,608 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
     </row>
     <row r="2" spans="1:7" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="12"/>
     </row>
     <row r="5" spans="1:7" ht="210" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="7" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="A7" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
     </row>
     <row r="8" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="F8" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="G8" s="28" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="132" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="29" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="G10" s="31" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="150" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="29" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="G12" s="31" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="29" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="27" t="s">
+      <c r="G14" s="31" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="29" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="31" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="G16" s="31" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="29" t="s">
         <v>74</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="F17" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="29" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="9"/>
-      <c r="E19" s="9"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
     </row>
     <row r="20" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="24" t="s">
+      <c r="A20" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="F20" s="24" t="s">
+      <c r="F20" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="G20" s="24" t="s">
+      <c r="G20" s="28" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="117.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="29" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="29" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F21" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="29" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="117.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="31" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="31" t="s">
         <v>91</v>
       </c>
-      <c r="F22" s="27" t="s">
+      <c r="F22" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="G22" s="27" t="s">
+      <c r="G22" s="31" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="117.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="D23" s="25" t="s">
+      <c r="D23" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="E23" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="F23" s="25" t="s">
+      <c r="F23" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="25" t="s">
+      <c r="G23" s="29" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="117.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="D24" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="F24" s="27" t="s">
+      <c r="F24" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="G24" s="27" t="s">
+      <c r="G24" s="31" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="117.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="29" t="s">
         <v>104</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="E25" s="25" t="s">
+      <c r="E25" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="F25" s="25" t="s">
+      <c r="F25" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="G25" s="25" t="s">
+      <c r="G25" s="29" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="117.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D26" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="E26" s="27" t="s">
+      <c r="E26" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="F26" s="27" t="s">
+      <c r="F26" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="G26" s="27" t="s">
+      <c r="G26" s="31" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="117.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="D27" s="25" t="s">
+      <c r="D27" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="E27" s="25" t="s">
+      <c r="E27" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="F27" s="25" t="s">
+      <c r="F27" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="G27" s="25" t="s">
+      <c r="G27" s="29" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="9" t="s">
+      <c r="A29" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="9"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="9"/>
-      <c r="G29" s="9"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
     </row>
     <row r="30" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="24" t="s">
+      <c r="A30" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D30" s="24" t="s">
+      <c r="D30" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E30" s="24"/>
-      <c r="F30" s="24"/>
-      <c r="G30" s="24"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28"/>
     </row>
     <row r="31" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
     </row>
     <row r="33" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
     </row>
     <row r="34" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
     </row>
     <row r="35" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="29" t="s">
         <v>133</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="29" t="s">
         <v>134</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C35" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
     </row>
     <row r="37" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2153,136 +2697,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
     </row>
     <row r="3" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="33" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="20">
         <v>1.1904831386747801</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="19">
         <v>1.4290507975078801</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="19">
         <v>1.3511465674354901</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="B5" s="19">
+      <c r="B5" s="22">
         <v>0.41818181818181799</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="21">
         <v>0.25454545454545502</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="21">
         <v>0.36363636363636398</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="23">
         <v>6144</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="23">
         <v>6144</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="24">
         <v>6144</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="19">
+      <c r="B7" s="22">
         <v>0.79361903667449996</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="21">
         <v>0.78387802839279197</v>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="21">
         <v>0.79090696573257502</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="21">
         <v>0.109090909090909</v>
       </c>
-      <c r="C8" s="19">
+      <c r="C8" s="22">
         <v>0.18181818181818199</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="21">
         <v>0.145454545454545</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="21">
         <v>0.300499707460403</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="21">
         <v>0.44934788346290599</v>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="22">
         <v>0.45541989803314198</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="21">
         <v>0.72727272727272696</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="22">
         <v>0.74545454545454604</v>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="22">
         <v>0.74545454545454604</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="25">
         <v>51.726512917605298</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="25">
         <v>62.809777008403401</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="26">
         <v>45.184126992659102</v>
       </c>
     </row>
@@ -2305,136 +2849,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
     </row>
     <row r="3" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="28" t="s">
+      <c r="A3" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="33" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="17">
+      <c r="B4" s="20">
         <v>1.1606829999999999</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="19">
         <v>1.1704939999999999</v>
       </c>
-      <c r="D4" s="16">
+      <c r="D4" s="19">
         <v>1.2153119999999999</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="21">
         <v>0.27272727272727298</v>
       </c>
-      <c r="C5" s="18">
+      <c r="C5" s="21">
         <v>0.218181818181818</v>
       </c>
-      <c r="D5" s="19">
+      <c r="D5" s="22">
         <v>0.36363636363636398</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="23">
         <v>6144</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="23">
         <v>6144</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="24">
         <v>6144</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="21">
         <v>0.81602418422698997</v>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="21">
         <v>0.82569217681884799</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="22">
         <v>0.82857364416122403</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="21">
         <v>5.4545454545454501E-2</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C8" s="21">
         <v>0.109090909090909</v>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="22">
         <v>0.145454545454545</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="21">
         <v>0.35609588027000399</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="22">
         <v>0.51160752773284901</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="21">
         <v>0.49508333206176802</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="19">
+      <c r="B10" s="22">
         <v>0.78181818181818197</v>
       </c>
-      <c r="C10" s="18">
+      <c r="C10" s="21">
         <v>0.74545454545454604</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="21">
         <v>0.70909090909090899</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="25">
         <v>51.332740107449602</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="25">
         <v>54.960852280530098</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="26">
         <v>49.8105536634272</v>
       </c>
     </row>
@@ -2460,608 +3004,608 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
     </row>
     <row r="4" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="210" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="7" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="5"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="30" t="s">
+      <c r="B8" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="34" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="132" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B9" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="25" t="s">
+      <c r="E9" s="29" t="s">
         <v>145</v>
       </c>
-      <c r="F9" s="25" t="s">
+      <c r="F9" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="G9" s="25" t="s">
+      <c r="G9" s="29" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="31" t="s">
         <v>149</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="F10" s="27" t="s">
+      <c r="F10" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="G10" s="31" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="150" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25" t="s">
+      <c r="A11" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="29" t="s">
         <v>151</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="29" t="s">
         <v>152</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="29" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="27" t="s">
+      <c r="F12" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="G12" s="31" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="D13" s="25" t="s">
+      <c r="D13" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="25" t="s">
+      <c r="E13" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="29" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="F14" s="27" t="s">
+      <c r="F14" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="G14" s="27" t="s">
+      <c r="G14" s="31" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="25" t="s">
+      <c r="D15" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="29" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="31" t="s">
         <v>166</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="F16" s="27" t="s">
+      <c r="F16" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="G16" s="31" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="29" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="D17" s="25" t="s">
+      <c r="D17" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="25" t="s">
+      <c r="F17" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="G17" s="25" t="s">
+      <c r="G17" s="29" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5"/>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="30" t="s">
+      <c r="A20" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="34" t="s">
         <v>76</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="D20" s="30" t="s">
+      <c r="D20" s="34" t="s">
         <v>78</v>
       </c>
-      <c r="E20" s="30" t="s">
+      <c r="E20" s="34" t="s">
         <v>79</v>
       </c>
-      <c r="F20" s="30" t="s">
+      <c r="F20" s="34" t="s">
         <v>80</v>
       </c>
-      <c r="G20" s="30" t="s">
+      <c r="G20" s="34" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="29" t="s">
         <v>139</v>
       </c>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="29" t="s">
         <v>174</v>
       </c>
-      <c r="D21" s="25" t="s">
+      <c r="D21" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="E21" s="25" t="s">
+      <c r="E21" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="F21" s="25" t="s">
+      <c r="F21" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="G21" s="25" t="s">
+      <c r="G21" s="29" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="31" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="31" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="31" t="s">
         <v>179</v>
       </c>
-      <c r="F22" s="27" t="s">
+      <c r="F22" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="G22" s="27" t="s">
+      <c r="G22" s="31" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="25" t="s">
+      <c r="B23" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="D23" s="25" t="s">
+      <c r="D23" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="E23" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="F23" s="25" t="s">
+      <c r="F23" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="25" t="s">
+      <c r="G23" s="29" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="31" t="s">
         <v>182</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="31" t="s">
         <v>98</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="D24" s="31" t="s">
         <v>99</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="F24" s="27" t="s">
+      <c r="F24" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="G24" s="27" t="s">
+      <c r="G24" s="31" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B25" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="E25" s="25" t="s">
+      <c r="E25" s="29" t="s">
         <v>85</v>
       </c>
-      <c r="F25" s="25" t="s">
+      <c r="F25" s="29" t="s">
         <v>86</v>
       </c>
-      <c r="G25" s="25" t="s">
+      <c r="G25" s="29" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="31" t="s">
         <v>108</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D26" s="31" t="s">
         <v>109</v>
       </c>
-      <c r="E26" s="27" t="s">
+      <c r="E26" s="31" t="s">
         <v>85</v>
       </c>
-      <c r="F26" s="27" t="s">
+      <c r="F26" s="31" t="s">
         <v>86</v>
       </c>
-      <c r="G26" s="27" t="s">
+      <c r="G26" s="31" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B27" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="D27" s="25" t="s">
+      <c r="D27" s="29" t="s">
         <v>113</v>
       </c>
-      <c r="E27" s="25" t="s">
+      <c r="E27" s="29" t="s">
         <v>114</v>
       </c>
-      <c r="F27" s="25" t="s">
+      <c r="F27" s="29" t="s">
         <v>115</v>
       </c>
-      <c r="G27" s="25" t="s">
+      <c r="G27" s="29" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
     </row>
     <row r="30" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C30" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
     </row>
     <row r="31" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="29" t="s">
         <v>119</v>
       </c>
-      <c r="B31" s="25" t="s">
+      <c r="B31" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="C31" s="25" t="s">
+      <c r="C31" s="29" t="s">
         <v>120</v>
       </c>
-      <c r="D31" s="7" t="s">
+      <c r="D31" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10"/>
+      <c r="G31" s="10"/>
     </row>
     <row r="32" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="31" t="s">
         <v>123</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="31" t="s">
         <v>124</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="E32" s="6"/>
-      <c r="F32" s="6"/>
-      <c r="G32" s="6"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
     </row>
     <row r="33" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="25" t="s">
+      <c r="A33" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="B33" s="25" t="s">
+      <c r="B33" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="C33" s="25" t="s">
+      <c r="C33" s="29" t="s">
         <v>128</v>
       </c>
-      <c r="D33" s="7" t="s">
+      <c r="D33" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
     </row>
     <row r="34" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="27" t="s">
+      <c r="A34" s="31" t="s">
         <v>130</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="C34" s="27" t="s">
+      <c r="C34" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
     </row>
     <row r="35" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="25" t="s">
+      <c r="A35" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="B35" s="25" t="s">
+      <c r="B35" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="C35" s="25" t="s">
+      <c r="C35" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="D35" s="7" t="s">
+      <c r="D35" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
     </row>
     <row r="37" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B37" s="10"/>
-      <c r="C37" s="10"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="10"/>
-      <c r="F37" s="10"/>
-      <c r="G37" s="10"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -3083,4 +3627,941 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:G68"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="5" max="5" width="40" customWidth="1"/>
+    <col min="6" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+    </row>
+    <row r="3" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+    </row>
+    <row r="4" spans="1:7" ht="94.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+    </row>
+    <row r="5" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>202</v>
+      </c>
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+    </row>
+    <row r="7" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>204</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="D7" s="27"/>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+    </row>
+    <row r="8" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" s="27"/>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="27"/>
+    </row>
+    <row r="9" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>210</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>211</v>
+      </c>
+      <c r="D9" s="27"/>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+    </row>
+    <row r="10" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+    </row>
+    <row r="11" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="D11" s="27"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+    </row>
+    <row r="12" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+    </row>
+    <row r="13" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>222</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>223</v>
+      </c>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+    </row>
+    <row r="14" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="B14" s="36" t="s">
+        <v>225</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="D14" s="27"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="27"/>
+    </row>
+    <row r="15" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>228</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>229</v>
+      </c>
+      <c r="D15" s="27"/>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+    </row>
+    <row r="16" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>232</v>
+      </c>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+    </row>
+    <row r="17" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>235</v>
+      </c>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+    </row>
+    <row r="18" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>238</v>
+      </c>
+      <c r="D18" s="27"/>
+      <c r="E18" s="27"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+    </row>
+    <row r="19" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>241</v>
+      </c>
+      <c r="D19" s="27"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+    </row>
+    <row r="20" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="C20" s="27" t="s">
+        <v>244</v>
+      </c>
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+    </row>
+    <row r="21" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>246</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+    </row>
+    <row r="23" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="35" t="s">
+        <v>249</v>
+      </c>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+    </row>
+    <row r="24" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="C24" s="27" t="s">
+        <v>252</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="E24" s="27"/>
+      <c r="F24" s="27"/>
+      <c r="G24" s="27"/>
+    </row>
+    <row r="25" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="C25" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>253</v>
+      </c>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+    </row>
+    <row r="26" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="27" t="s">
+        <v>257</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="C26" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="E26" s="27"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="27"/>
+    </row>
+    <row r="27" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+    </row>
+    <row r="28" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="11"/>
+      <c r="E28" s="11"/>
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+    </row>
+    <row r="29" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="35" t="s">
+        <v>263</v>
+      </c>
+      <c r="B29" s="35" t="s">
+        <v>264</v>
+      </c>
+      <c r="C29" s="35"/>
+      <c r="D29" s="35"/>
+      <c r="E29" s="35"/>
+      <c r="F29" s="35"/>
+      <c r="G29" s="35"/>
+    </row>
+    <row r="30" spans="1:7" ht="189.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>266</v>
+      </c>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="E30" s="27"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+    </row>
+    <row r="31" spans="1:7" ht="210" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C31" s="27"/>
+      <c r="D31" s="27"/>
+      <c r="E31" s="27"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+    </row>
+    <row r="32" spans="1:7" ht="210" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="27" t="s">
+        <v>269</v>
+      </c>
+      <c r="B32" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="C32" s="27"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+    </row>
+    <row r="33" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+    </row>
+    <row r="34" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+    </row>
+    <row r="35" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="11"/>
+      <c r="E35" s="11"/>
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+    </row>
+    <row r="36" spans="1:7" ht="150" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+    </row>
+    <row r="37" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+    </row>
+    <row r="38" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+    </row>
+    <row r="39" spans="1:7" ht="84.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="11" t="s">
+        <v>277</v>
+      </c>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="11"/>
+      <c r="E39" s="11"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+    </row>
+    <row r="40" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="35" t="s">
+        <v>278</v>
+      </c>
+      <c r="B40" s="35" t="s">
+        <v>279</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>280</v>
+      </c>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="35"/>
+    </row>
+    <row r="41" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27" t="s">
+        <v>281</v>
+      </c>
+      <c r="B41" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C41" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+    </row>
+    <row r="42" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="B42" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C42" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+    </row>
+    <row r="43" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="B43" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C43" s="27" t="s">
+        <v>287</v>
+      </c>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+    </row>
+    <row r="44" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="27" t="s">
+        <v>288</v>
+      </c>
+      <c r="B44" s="27" t="s">
+        <v>289</v>
+      </c>
+      <c r="C44" s="27" t="s">
+        <v>290</v>
+      </c>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+    </row>
+    <row r="45" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+    </row>
+    <row r="46" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+    </row>
+    <row r="47" spans="1:7" ht="199.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+    </row>
+    <row r="48" spans="1:7" ht="109.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="11" t="s">
+        <v>294</v>
+      </c>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+    </row>
+    <row r="49" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" spans="1:7" ht="84.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="11" t="s">
+        <v>296</v>
+      </c>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+    </row>
+    <row r="51" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="B51" s="35" t="s">
+        <v>298</v>
+      </c>
+      <c r="C51" s="35"/>
+      <c r="D51" s="35"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="35"/>
+      <c r="G51" s="35"/>
+    </row>
+    <row r="52" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="27" t="s">
+        <v>299</v>
+      </c>
+      <c r="B52" s="27" t="s">
+        <v>300</v>
+      </c>
+      <c r="C52" s="27"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="27"/>
+    </row>
+    <row r="53" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="27" t="s">
+        <v>301</v>
+      </c>
+      <c r="B53" s="27" t="s">
+        <v>302</v>
+      </c>
+      <c r="C53" s="27"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+    </row>
+    <row r="54" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="27" t="s">
+        <v>303</v>
+      </c>
+      <c r="B54" s="27" t="s">
+        <v>304</v>
+      </c>
+      <c r="C54" s="27"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="27"/>
+    </row>
+    <row r="55" spans="1:7" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="27" t="s">
+        <v>305</v>
+      </c>
+      <c r="B55" s="27" t="s">
+        <v>306</v>
+      </c>
+      <c r="C55" s="27"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="27"/>
+      <c r="G55" s="27"/>
+    </row>
+    <row r="56" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+    </row>
+    <row r="57" spans="1:7" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+    </row>
+    <row r="58" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="35" t="s">
+        <v>309</v>
+      </c>
+      <c r="B58" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C58" s="35"/>
+      <c r="D58" s="35"/>
+      <c r="E58" s="35"/>
+      <c r="F58" s="35"/>
+      <c r="G58" s="35"/>
+    </row>
+    <row r="59" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="B59" s="27" t="s">
+        <v>312</v>
+      </c>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+    </row>
+    <row r="60" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="27" t="s">
+        <v>313</v>
+      </c>
+      <c r="B60" s="27" t="s">
+        <v>314</v>
+      </c>
+      <c r="C60" s="27"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="27"/>
+      <c r="G60" s="27"/>
+    </row>
+    <row r="61" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="27" t="s">
+        <v>315</v>
+      </c>
+      <c r="B61" s="27" t="s">
+        <v>316</v>
+      </c>
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+    </row>
+    <row r="62" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="27" t="s">
+        <v>317</v>
+      </c>
+      <c r="B62" s="27" t="s">
+        <v>318</v>
+      </c>
+      <c r="C62" s="27"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="27"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="27"/>
+    </row>
+    <row r="63" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="27" t="s">
+        <v>319</v>
+      </c>
+      <c r="B63" s="27" t="s">
+        <v>320</v>
+      </c>
+      <c r="C63" s="27"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="27"/>
+      <c r="F63" s="27"/>
+      <c r="G63" s="27"/>
+    </row>
+    <row r="64" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="27" t="s">
+        <v>321</v>
+      </c>
+      <c r="B64" s="27" t="s">
+        <v>322</v>
+      </c>
+      <c r="C64" s="27"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="27"/>
+    </row>
+    <row r="65" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="27" t="s">
+        <v>323</v>
+      </c>
+      <c r="B65" s="27" t="s">
+        <v>324</v>
+      </c>
+      <c r="C65" s="27"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="27"/>
+      <c r="F65" s="27"/>
+      <c r="G65" s="27"/>
+    </row>
+    <row r="66" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="B66" s="27" t="s">
+        <v>326</v>
+      </c>
+      <c r="C66" s="27"/>
+      <c r="D66" s="27"/>
+      <c r="E66" s="27"/>
+      <c r="F66" s="27"/>
+      <c r="G66" s="27"/>
+    </row>
+    <row r="67" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="27" t="s">
+        <v>327</v>
+      </c>
+      <c r="B67" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="C67" s="27"/>
+      <c r="D67" s="27"/>
+      <c r="E67" s="27"/>
+      <c r="F67" s="27"/>
+      <c r="G67" s="27"/>
+    </row>
+    <row r="68" spans="1:7" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="27" t="s">
+        <v>329</v>
+      </c>
+      <c r="B68" s="27" t="s">
+        <v>330</v>
+      </c>
+      <c r="C68" s="27"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="27"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A49:G49"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="A36:G36"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A33:G33"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
 </file>